--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -1,29 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShalaTeam" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ShalaTeam" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -42,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -440,274 +396,180 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Photo</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Position</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Group</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Photo</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Shweta Chaudhari</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Shala Principal</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Shala Management</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/shweta-chaudhari.jpg</t>
-        </is>
+      <c r="A2" t="str">
+        <v>Shweta Chaudhari</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Shala Principal</v>
+      </c>
+      <c r="C2" t="str">
+        <v xml:space="preserve"> Shala Management</v>
+      </c>
+      <c r="D2" t="str">
+        <v>assets/images/shala/team/shweta-chaudhari.jpg</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Aaditi Dixit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Shala Vice Principal</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Shala Management</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/aaditi-dixit.jpg</t>
-        </is>
+      <c r="A3" t="str">
+        <v>Aaditi Dixit</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Shala Management</v>
+      </c>
+      <c r="D3" t="str">
+        <v>assets/images/shala/team/aaditi-dixit.jpg</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ravindra Kadam</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Shala Engagement Manager (Volunteer)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Shala Management</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/ravindra-kadam.jpg</t>
-        </is>
+      <c r="A4" t="str">
+        <v>Ravindra Kadam</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Shala Engagement Manager (Volunteer)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Shala Management</v>
+      </c>
+      <c r="D4" t="str">
+        <v>assets/images/shala/team/ravindra-kadam.jpg</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Harshada Joshi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/harshada-joshi.jpg</t>
-        </is>
+      <c r="A5" t="str">
+        <v>Harshada Joshi</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D5" t="str">
+        <v>assets/images/shala/team/harshada-joshi.jpg</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Aashlesha Kshirsagar</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/aashlesha-kshirsagar.jpg</t>
-        </is>
+      <c r="A6" t="str">
+        <v>Aashlesha Kshirsagar</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D6" t="str">
+        <v>assets/images/shala/team/aashlesha-kshirsagar.jpg</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Minal Oak</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/minal-oak.jpg</t>
-        </is>
+      <c r="A7" t="str">
+        <v>Minal Oak</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D7" t="str">
+        <v>assets/images/shala/team/minal-oak.jpg</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Manisha Rahatadkar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/manisha-rahatadkar.jpg</t>
-        </is>
+      <c r="A8" t="str">
+        <v>Manisha Rahatadkar</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Shala Vice Principal</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D8" t="str">
+        <v>assets/images/shala/team/manisha-rahatadkar.jpg</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Komal Kadam</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/komal-kadam.jpg</t>
-        </is>
+      <c r="A9" t="str">
+        <v>Komal Kadam</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D9" t="str">
+        <v>assets/images/shala/team/komal-kadam.jpg</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Madhura Kulkarni</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
+      <c r="A10" t="str">
+        <v>Madhura Kulkarni</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Divya Chaudhari</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/divya-chaudhari.jpg</t>
-        </is>
+      <c r="A11" t="str">
+        <v>Divya Chaudhari</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D11" t="str">
+        <v>assets/images/shala/team/divya-chaudhari.jpg</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Vinita Kotnis</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Teacher</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>assets/images/shala/team/vinita-kotnis.jpg</t>
-        </is>
+      <c r="A12" t="str">
+        <v>Vinita Kotnis</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D12" t="str">
+        <v>assets/images/shala/team/vinita-kotnis.jpg</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -459,7 +459,7 @@
         <v>Shala Vice Principal</v>
       </c>
       <c r="C3" t="str">
-        <v>Teachers</v>
+        <v>Shala Management</v>
       </c>
       <c r="D3" t="str">
         <v>assets/images/shala/team/manisha-rahatadkar.jpg</v>
@@ -511,7 +511,7 @@
         <v>Teacher</v>
       </c>
       <c r="C5" t="str">
-        <v>Shala Management</v>
+        <v>Teachers</v>
       </c>
       <c r="D5" t="str">
         <v>assets/images/shala/team/aaditi-dixit.jpg</v>

--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -711,9 +711,61 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Rashmi</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Thakare</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D13" t="str">
+        <v>assets/images/shala/team/Rashmi-Thakare.jpeg</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Gauri</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Savanur</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Teachers</v>
+      </c>
+      <c r="D14" t="str">
+        <v>assets/images/shala/team/Gauri-Savanur.jpeg</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -719,7 +719,7 @@
         <v>Thakare</v>
       </c>
       <c r="C13" t="str">
-        <v>Teachers</v>
+        <v>Teacher</v>
       </c>
       <c r="D13" t="str">
         <v>assets/images/shala/team/Rashmi-Thakare.jpeg</v>
@@ -745,7 +745,7 @@
         <v>Savanur</v>
       </c>
       <c r="C14" t="str">
-        <v>Teachers</v>
+        <v>Teacher</v>
       </c>
       <c r="D14" t="str">
         <v>assets/images/shala/team/Gauri-Savanur.jpeg</v>

--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -722,7 +722,7 @@
         <v>Teacher</v>
       </c>
       <c r="D13" t="str">
-        <v>assets/images/shala/team/Rashmi-Thakare.jpeg</v>
+        <v>assets/images/shala/team/Rashmi-Thakare.jpg</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -734,38 +734,12 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Gauri</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Savanur</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Teacher</v>
-      </c>
-      <c r="D14" t="str">
-        <v>assets/images/shala/team/Gauri-Savanur.jpeg</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -737,9 +737,35 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Gauri</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Savanur</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="D14" t="str">
+        <v>assets/images/shala/team/Gauri-Savanur.jpg</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -719,10 +719,10 @@
         <v>Thakare</v>
       </c>
       <c r="C13" t="str">
-        <v>Teacher</v>
+        <v>Teachers</v>
       </c>
       <c r="D13" t="str">
-        <v>assets/images/shala/team/Rashmi-Thakare.jpg</v>
+        <v>assets/images/shala/team/Rashmi-Thakare.jpeg</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -745,10 +745,10 @@
         <v>Savanur</v>
       </c>
       <c r="C14" t="str">
-        <v>Teacher</v>
+        <v>Teachers</v>
       </c>
       <c r="D14" t="str">
-        <v>assets/images/shala/team/Gauri-Savanur.jpg</v>
+        <v>assets/images/shala/team/Gauri-Savanur.jpeg</v>
       </c>
       <c r="E14" t="str">
         <v/>

--- a/data/shala-team.xlsx
+++ b/data/shala-team.xlsx
@@ -713,10 +713,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Rashmi</v>
+        <v>Rashmi Thakare</v>
       </c>
       <c r="B13" t="str">
-        <v>Thakare</v>
+        <v>Teacher</v>
       </c>
       <c r="C13" t="str">
         <v>Teachers</v>
@@ -739,10 +739,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Gauri</v>
+        <v>Gauri Savanur</v>
       </c>
       <c r="B14" t="str">
-        <v>Savanur</v>
+        <v>Teacher</v>
       </c>
       <c r="C14" t="str">
         <v>Teachers</v>
